--- a/sr007_leads_report.xlsx
+++ b/sr007_leads_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>manual_web_search</t>
+          <t>google, manual_web_search</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>manual_web_search</t>
+          <t>linkedin_post, manual_web_search</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>manual_web_search</t>
+          <t>linkedin_people_search, linkedin_post, manual_web_search</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Two separate LinkedIn posts from team members explicitly state DRS joined a16z speedrun SR007.</t>
+          <t>Two individuals (co-founders) explicitly state DRS has joined a16z speedrun SR007.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>google, manual_web_search</t>
+          <t>google, linkedin_post, manual_web_search</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Founder's LinkedIn headline explicitly states 'building Philyron (a16z SR007)'.</t>
+          <t>Founder Heon Lee explicitly states he is building Philyron as part of a16z SR007.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Co-founder explicitly states Rumbo AI is part of a16z SR007.</t>
+          <t>Co-founder explicitly states Rumbo AI was selected for a16z SR007.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>google, linkedin_post</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Team member post explicitly confirms Vene Health is officially part of SR007.</t>
+          <t>Team member states Vene Health is officially part of a16z Speedrun SR007.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>google, linkedin_post</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Same company (Vene Health) confirmed as SR007 via founder and company LinkedIn posts.</t>
+          <t>Same company as Vene Health, confirmed via founder/company posts about SR007 inclusion.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Multiple team members' LinkedIn profiles/posts explicitly tag Building Blueprint as a16z SR007.</t>
+          <t>Founder announces $1M raise led by a16z speedrun and LinkedIn headline confirms SR007 membership.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Co-founder's LinkedIn headline explicitly states PreMan is part of a16z speedrun SR007.</t>
+          <t>Co-founder's LinkedIn headline explicitly states 'Cofounder @ PreMan (a16z speedrun SR007)'.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -936,30 +936,471 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Tenera</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>a16z Speedrun's own LinkedIn post announces Tenera is now backed by a16z speedrun as part of SR007.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>google, linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>a16z speedrun Employees, Location, Alumni
+LinkedIn · a16z speedrun
+Ca. 62.890 Follower CEO &amp; Co-founder @ Tenera (a16z SR007) | ex-Uber, Stanford. 2w. Report this post; Close menu. Excited to announce that Tenera is now backed by a16z speedrun!</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder's LinkedIn headline and post thank a16z speedrun for backing Space as part of SR007.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>google, linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Andreessen Horowitz leads Space Computer Inc. $2.4MM ...
+LinkedIn · Silicon Legal Strategy
+Ca. 10 Reaktionen · vor 6 Tagen Co-Founder @Space (a16z SR007) | Engineer, Filmmaker, YouTuber ... thanks a16z speedrun for backing us, and to Jason Zhao and Arihant ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Building Vene</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Founder Aritra Saha states Vene is officially part of SR007.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search, linkedin_post</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Feed post
+Aritra Saha
+  • 2nd
+Building Vene (SR007) | Prev @ xAI, Apple  | CS @ Georgia Tech
+6d • 
+Follow
+A few months ago I posted that I turned down Y Combinator for something that fit us better, and that I couldn't say what it was yet.
+This is it.
+is officially part of(SR007).
+Vene is a proactive health assistant that runs healthcare for you. It calls between visits to check in on meals, me</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Hoid</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Multiple co-founders list themselves as Co-founder @ Hoid (SR007).</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Pavle Padjin 
+ • 2nd
+Co-founder @ Hoid (SR007) | CS @ University of Cambridge
+Belgrade, Serbia
+Connect
+Leonardo Vanni &amp; Ayaan Parikh are mutual connections</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Blueprint</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; COO explicitly lists Blueprint as a16z SR007 company.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Sajeel Purewal 
+ • 2nd
+Co-Founder &amp; COO at Blueprint (a16z SR007)
+Greater Toronto Area, Canada
+Connect
+Jef Guo is a mutual connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Whispr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Founding engineer identifies openWhispr as a16z SR007 company, matching Whispr.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Chad Piha 
+ • 3rd+
+Founding AI Engineer @ openWhispr (a16z SR007) | Co-Founder @ Thirsty Bird
+San Francisco Bay Area
+Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Mecone</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Multiple co-founders identify themselves as Co-Founder of Mecone / a16z speedrun 007.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Alexander Wesley 
+ • 2nd
+Co-Founder of Mecone / a16z speedrun 007
+San Francisco Bay Area
+Connect
+Kasper Johansson, Simmi Sen &amp; 3 other mutual connections</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Zorbe</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Multiple co-founders' LinkedIn headlines explicitly state Zorbe is part of a16z SR007.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Yash Iyer 
+ • 2nd
+Co-founder, Zorbe (a16z sr007) | prev. Wharton + CS @ Penn
+San Francisco Bay Area
+Connect
+Sandhya Mahesh, Simmi Sen &amp; 4 other mutual connections</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Alven</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Multiple co-founders' LinkedIn headlines explicitly state Alven is part of a16z SR007.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Julio-Cezar Scerbina • 2nd
+Co-founder &amp; CEO @ Alven(a16Z sr007)
+San Francisco, California, United States
+Follow
+Yasin Ehsan, Celeste Amadon &amp; 1 other mutual connection
+ · 6K followers</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Baro</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder &amp; CEO explicitly states affiliation with a16z SR007.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Brian Cho 
+ • 3rd+
+Co-Founder &amp; CEO @ Baro, a16z SR007
+New York, New York, United States
+Follow
+2K followers</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SenseLab</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder explicitly states SenseLab is part of a16z Speedrun SR007.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Dai M. 
+ • 3rd+
+Building continuous learning for AI agents. Co-founder @SenseLab  - a16z Speedrun SR007
+Mountain View, California, United States
+Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder explicitly states Mirai is part of a16z SR007.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>linkedin_people_search</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Caleb Lo 
+ • 3rd+
+co-founder @ Mirai (a16z sr007)
+San Francisco Bay Area
+Follow
+2K followers
+Visit my website</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>Mariana Minerals</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>UNCERTAIN</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Only third-party aggregator blog lists it as SR007, not a founder or a16z staff statement.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Aug 25, 2026</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Only appears in a third-party aggregator list, not a direct founder or a16z staff confirmation.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>google</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>a16z Speedrun SR007 - all 29 companies, before demo day | frontrun
 frontrun.vc
